--- a/docs/erd/Kamus Data ERD SPMB SDN Jatimulya 04.xlsx
+++ b/docs/erd/Kamus Data ERD SPMB SDN Jatimulya 04.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daftar Entitas'!$A$4:$D$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kamus Data'!$A$4:$H$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kamus Data'!$A$4:$H$113</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Relasi'!$A$4:$H$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Enum &amp; Aturan'!$A$4:$C$34</definedName>
   </definedNames>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -881,19 +881,15 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>username</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>varchar(120)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
+          <t>varchar(50)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -902,7 +898,7 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Alamat email untuk login (unik)</t>
+          <t>Nama pengguna untuk login; boleh nama sendiri dengan spasi, 3–50 karakter, unik tanpa membedakan huruf besar/kecil</t>
         </is>
       </c>
     </row>
@@ -917,24 +913,28 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>no_hp</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>varchar(15)</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>varchar(120)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Nomor HP/WhatsApp, diawali 08</t>
+          <t>Alamat email (opsional, unik bila diisi); untuk tautan lupa kata sandi dan dapat dipakai untuk login</t>
         </is>
       </c>
     </row>
@@ -949,12 +949,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>password_hash</t>
+          <t>no_hp</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>varchar(15)</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr"/>
@@ -966,7 +966,7 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Kata sandi yang sudah di-hash (bcrypt), bukan teks asli</t>
+          <t>Nomor HP/WhatsApp, diawali 08</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>peran</t>
+          <t>password_hash</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>peran_pengguna</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -995,14 +995,10 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>'orang_tua'</t>
-        </is>
-      </c>
+      <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Peran pengguna: orang_tua, panitia, kepala_sekolah, admin</t>
+          <t>Kata sandi yang sudah di-hash (bcrypt), bukan teks asli</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1013,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>aktif</t>
+          <t>peran</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>peran_pengguna</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr"/>
@@ -1033,12 +1029,12 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>'orang_tua'</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Status akun; false = dinonaktifkan admin dan tidak dapat login</t>
+          <t>Peran pengguna: orang_tua, panitia, kepala_sekolah, admin</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1049,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>dibuat_pada</t>
+          <t>aktif</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -1069,88 +1065,88 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Status akun; false = dinonaktifkan admin dan tidak dapat login</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>PENGGUNA</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>dibuat_pada</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Waktu data dibuat</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>PERIODE_SPMB</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.periode_spmb_id_seq)</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>PERIODE_SPMB</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>tahun_ajaran</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>varchar(9)</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Tahun ajaran, contoh 2026/2027</t>
         </is>
       </c>
     </row>
@@ -1161,19 +1157,23 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>tgl_mulai_daftar</t>
+          <t>tahun_ajaran</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
+          <t>varchar(9)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -1182,7 +1182,7 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Tanggal mulai pendaftaran</t>
+          <t>Tahun ajaran, contoh 2026/2027</t>
         </is>
       </c>
     </row>
@@ -1193,11 +1193,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>tgl_selesai_daftar</t>
+          <t>tgl_mulai_daftar</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1214,7 +1214,7 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Tanggal akhir pendaftaran</t>
+          <t>Tanggal mulai pendaftaran</t>
         </is>
       </c>
     </row>
@@ -1225,11 +1225,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>tgl_pengumuman</t>
+          <t>tgl_selesai_daftar</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1246,7 +1246,7 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Tanggal pengumuman hasil</t>
+          <t>Tanggal akhir pendaftaran</t>
         </is>
       </c>
     </row>
@@ -1257,11 +1257,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>tgl_daftar_ulang_mulai</t>
+          <t>tgl_pengumuman</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Tanggal mulai daftar ulang</t>
+          <t>Tanggal pengumuman hasil</t>
         </is>
       </c>
     </row>
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>tgl_daftar_ulang_selesai</t>
+          <t>tgl_daftar_ulang_mulai</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1310,7 +1310,7 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Tanggal akhir daftar ulang</t>
+          <t>Tanggal mulai daftar ulang</t>
         </is>
       </c>
     </row>
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>tgl_acuan_usia</t>
+          <t>tgl_daftar_ulang_selesai</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1342,7 +1342,7 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Tanggal acuan perhitungan usia (1 Juli tahun berjalan)</t>
+          <t>Tanggal akhir daftar ulang</t>
         </is>
       </c>
     </row>
@@ -1353,16 +1353,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>jumlah_rombel</t>
+          <t>tgl_acuan_usia</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Jumlah rombongan belajar kelas 1</t>
+          <t>Tanggal acuan perhitungan usia (1 Juli tahun berjalan)</t>
         </is>
       </c>
     </row>
@@ -1385,11 +1385,11 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>murid_per_rombel</t>
+          <t>jumlah_rombel</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Jumlah murid per rombel (maks. 28)</t>
+          <t>Jumlah rombongan belajar kelas 1</t>
         </is>
       </c>
     </row>
@@ -1417,11 +1417,11 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>daya_tampung</t>
+          <t>murid_per_rombel</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1432,17 +1432,13 @@
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>GENERATED: (jumlah_rombel * murid_per_rombel)</t>
-        </is>
-      </c>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Kolom terhitung: jumlah_rombel × murid_per_rombel</t>
+          <t>Jumlah murid per rombel (maks. 28)</t>
         </is>
       </c>
     </row>
@@ -1453,32 +1449,32 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>aktif</t>
+          <t>daya_tampung</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>GENERATED: (jumlah_rombel * murid_per_rombel)</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Penanda periode yang sedang berjalan (hanya satu yang aktif)</t>
+          <t>Kolom terhitung: jumlah_rombel × murid_per_rombel</t>
         </is>
       </c>
     </row>
@@ -1489,28 +1485,32 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>seleksi_diproses_pada</t>
+          <t>aktif</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Waktu panitia menetapkan hasil seleksi</t>
+          <t>Penanda periode yang sedang berjalan (hanya satu yang aktif)</t>
         </is>
       </c>
     </row>
@@ -1521,108 +1521,104 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>hasil_diumumkan</t>
+          <t>seleksi_diproses_pada</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>timestamptz</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Waktu panitia menetapkan hasil seleksi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PERIODE_SPMB</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>hasil_diumumkan</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Penanda hasil seleksi sudah dipublikasikan (mengunci pengaturan)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>KUOTA_JALUR</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.kuota_jalur_id_seq)</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>KUOTA_JALUR</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>periode_id</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>UK, FK → periode_spmb</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Periode SPMB terkait</t>
         </is>
       </c>
     </row>
@@ -1633,21 +1629,21 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>jalur</t>
+          <t>periode_id</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>jalur_spmb</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UK, FK → periode_spmb</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -1658,7 +1654,7 @@
       <c r="G29" s="4" t="inlineStr"/>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Jalur pendaftaran: domisili, afirmasi, mutasi</t>
+          <t>Periode SPMB terkait</t>
         </is>
       </c>
     </row>
@@ -1669,19 +1665,23 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>persen</t>
+          <t>jalur</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>numeric(5,2)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
+          <t>jalur_spmb</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -1690,83 +1690,79 @@
       <c r="G30" s="4" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
+          <t>Jalur pendaftaran: domisili, afirmasi, mutasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>KUOTA_JALUR</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>persen</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>numeric(5,2)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
           <t>Persentase kuota jalur dari daya tampung</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>JENIS_DOKUMEN</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.jenis_dokumen_id_seq)</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>JENIS_DOKUMEN</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>kode</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>varchar(30)</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>Kode singkat jenis dokumen, contoh KK, AKTA</t>
         </is>
       </c>
     </row>
@@ -1777,19 +1773,23 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>nama</t>
+          <t>kode</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>varchar(120)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>varchar(30)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -1798,79 +1798,75 @@
       <c r="G33" s="4" t="inlineStr"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
+          <t>Kode singkat jenis dokumen, contoh KK, AKTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>JENIS_DOKUMEN</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>nama</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>varchar(120)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
           <t>Nama jenis dokumen</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>PERSYARATAN_JALUR</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B35" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>jalur</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>jalur_spmb</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>Jalur pendaftaran: domisili, afirmasi, mutasi</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>PERSYARATAN_JALUR</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>jenis_dokumen_id</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>PK, FK → jenis_dokumen</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Jenis dokumen terkait</t>
         </is>
       </c>
     </row>
@@ -1881,108 +1877,108 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>jenis_dokumen_id</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>PK, FK → jenis_dokumen</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Jenis dokumen terkait</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>PERSYARATAN_JALUR</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>wajib</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>Apakah dokumen wajib untuk jalur tersebut</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>CALON_MURID</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.calon_murid_id_seq)</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>CALON_MURID</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>pengguna_id</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>FK → pengguna</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>Akun orang tua/wali pemilik data</t>
         </is>
       </c>
     </row>
@@ -1993,21 +1989,21 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>nik</t>
+          <t>pengguna_id</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>character(16)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>FK → pengguna</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2018,7 +2014,7 @@
       <c r="G39" s="4" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Nomor Induk Kependudukan (16 digit)</t>
+          <t>Akun orang tua/wali pemilik data</t>
         </is>
       </c>
     </row>
@@ -2029,28 +2025,32 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>nisn</t>
+          <t>nik</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>character(10)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
+          <t>character(16)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Nomor Induk Siswa Nasional (10 digit, opsional)</t>
+          <t>Nomor Induk Kependudukan (16 digit)</t>
         </is>
       </c>
     </row>
@@ -2061,28 +2061,28 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>nama_lengkap</t>
+          <t>nisn</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>character(10)</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Nama lengkap sesuai akta</t>
+          <t>Nomor Induk Siswa Nasional (10 digit, opsional)</t>
         </is>
       </c>
     </row>
@@ -2093,16 +2093,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>jenis_kelamin</t>
+          <t>nama_lengkap</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>jenis_kelamin</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       <c r="G42" s="4" t="inlineStr"/>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>L atau P</t>
+          <t>Nama lengkap sesuai akta</t>
         </is>
       </c>
     </row>
@@ -2125,16 +2125,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>tempat_lahir</t>
+          <t>jenis_kelamin</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>varchar(60)</t>
+          <t>jenis_kelamin</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       <c r="G43" s="4" t="inlineStr"/>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Tempat lahir</t>
+          <t>L atau P</t>
         </is>
       </c>
     </row>
@@ -2157,16 +2157,16 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>tanggal_lahir</t>
+          <t>tempat_lahir</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>varchar(60)</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr"/>
@@ -2178,7 +2178,7 @@
       <c r="G44" s="4" t="inlineStr"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Tanggal lahir (dasar hitung usia)</t>
+          <t>Tempat lahir</t>
         </is>
       </c>
     </row>
@@ -2189,16 +2189,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>no_akta_lahir</t>
+          <t>tanggal_lahir</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr"/>
@@ -2210,7 +2210,7 @@
       <c r="G45" s="4" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Nomor registrasi akta kelahiran</t>
+          <t>Tanggal lahir (dasar hitung usia)</t>
         </is>
       </c>
     </row>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>agama</t>
+          <t>no_akta_lahir</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr"/>
@@ -2242,7 +2242,7 @@
       <c r="G46" s="4" t="inlineStr"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Agama</t>
+          <t>Nomor registrasi akta kelahiran</t>
         </is>
       </c>
     </row>
@@ -2253,16 +2253,16 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>kewarganegaraan</t>
+          <t>agama</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr"/>
@@ -2271,14 +2271,10 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>'Indonesia'</t>
-        </is>
-      </c>
+      <c r="G47" s="4" t="inlineStr"/>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Kewarganegaraan (default WNI)</t>
+          <t>Agama</t>
         </is>
       </c>
     </row>
@@ -2289,16 +2285,16 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>alamat</t>
+          <t>kewarganegaraan</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr"/>
@@ -2307,10 +2303,14 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>'Indonesia'</t>
+        </is>
+      </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Alamat jalan/kampung</t>
+          <t>Kewarganegaraan (default WNI)</t>
         </is>
       </c>
     </row>
@@ -2321,16 +2321,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>rt</t>
+          <t>alamat</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>character(3)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr"/>
@@ -2342,7 +2342,7 @@
       <c r="G49" s="4" t="inlineStr"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Alamat jalan/kampung</t>
         </is>
       </c>
     </row>
@@ -2353,11 +2353,11 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>rw</t>
+          <t>rt</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2374,7 +2374,7 @@
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RT</t>
         </is>
       </c>
     </row>
@@ -2385,16 +2385,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>kelurahan</t>
+          <t>rw</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>varchar(60)</t>
+          <t>character(3)</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
       <c r="G51" s="4" t="inlineStr"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Kelurahan/desa</t>
+          <t>RW</t>
         </is>
       </c>
     </row>
@@ -2417,11 +2417,11 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>kecamatan</t>
+          <t>kelurahan</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2438,7 +2438,7 @@
       <c r="G52" s="4" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>Kecamatan</t>
+          <t>Kelurahan/desa</t>
         </is>
       </c>
     </row>
@@ -2449,28 +2449,28 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>kode_pos</t>
+          <t>kecamatan</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>character(5)</t>
+          <t>varchar(60)</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Kode pos 5 digit</t>
+          <t>Kecamatan</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2481,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>patokan_rumah</t>
+          <t>kode_pos</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>varchar(150)</t>
+          <t>character(5)</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
@@ -2502,7 +2502,7 @@
       <c r="G54" s="4" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Patokan/ciri rumah (Dapodik butir 14)</t>
+          <t>Kode pos 5 digit</t>
         </is>
       </c>
     </row>
@@ -2513,16 +2513,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>tempat_tinggal</t>
+          <t>patokan_rumah</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>varchar(20)</t>
+          <t>varchar(150)</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Tempat tinggal: rumah_sendiri, orang_tua, saudara (butir 15)</t>
+          <t>Patokan/ciri rumah (Dapodik butir 14)</t>
         </is>
       </c>
     </row>
@@ -2545,16 +2545,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>moda_transportasi</t>
+          <t>tempat_tinggal</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>varchar(20)</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr"/>
@@ -2566,7 +2566,7 @@
       <c r="G56" s="4" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Moda transportasi ke sekolah (butir 16)</t>
+          <t>Tempat tinggal: rumah_sendiri, orang_tua, saudara (butir 15)</t>
         </is>
       </c>
     </row>
@@ -2577,28 +2577,28 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>no_kk</t>
+          <t>moda_transportasi</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>character(16)</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Nomor Kartu Keluarga (16 digit)</t>
+          <t>Moda transportasi ke sekolah (butir 16)</t>
         </is>
       </c>
     </row>
@@ -2609,16 +2609,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>tgl_terbit_kk</t>
+          <t>no_kk</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>character(16)</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
       <c r="G58" s="4" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Tanggal terbit KK (syarat domisili ≥ 1 tahun)</t>
+          <t>Nomor Kartu Keluarga (16 digit)</t>
         </is>
       </c>
     </row>
@@ -2641,28 +2641,28 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>jarak_ke_sekolah_km</t>
+          <t>tgl_terbit_kk</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>numeric(5,2)</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Jarak rumah ke sekolah dalam km</t>
+          <t>Tanggal terbit KK (syarat domisili ≥ 1 tahun)</t>
         </is>
       </c>
     </row>
@@ -2673,16 +2673,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>anak_ke</t>
+          <t>jarak_ke_sekolah_km</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>numeric(5,2)</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr"/>
@@ -2694,7 +2694,7 @@
       <c r="G60" s="4" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Anak ke-</t>
+          <t>Jarak rumah ke sekolah dalam km</t>
         </is>
       </c>
     </row>
@@ -2705,11 +2705,11 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>jumlah_saudara</t>
+          <t>anak_ke</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       <c r="G61" s="4" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Jumlah saudara kandung</t>
+          <t>Anak ke-</t>
         </is>
       </c>
     </row>
@@ -2737,16 +2737,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>no_kks</t>
+          <t>jumlah_saudara</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr"/>
@@ -2758,7 +2758,7 @@
       <c r="G62" s="4" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Nomor Kartu Keluarga Sejahtera (jalur afirmasi)</t>
+          <t>Jumlah saudara kandung</t>
         </is>
       </c>
     </row>
@@ -2769,32 +2769,28 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>penerima_pkh</t>
+          <t>no_kks</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Penerima Program Keluarga Harapan</t>
+          <t>Nomor Kartu Keluarga Sejahtera (jalur afirmasi)</t>
         </is>
       </c>
     </row>
@@ -2805,28 +2801,32 @@
         </is>
       </c>
       <c r="B64" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>no_kip</t>
+          <t>penerima_pkh</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>Nomor Kartu Indonesia Pintar</t>
+          <t>Penerima Program Keluarga Harapan</t>
         </is>
       </c>
     </row>
@@ -2837,11 +2837,11 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>no_kis_pbi</t>
+          <t>no_kip</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2858,7 +2858,7 @@
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Nomor KIS Penerima Bantuan Iuran (butir 20)</t>
+          <t>Nomor Kartu Indonesia Pintar</t>
         </is>
       </c>
     </row>
@@ -2869,16 +2869,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>tinggi_badan_cm</t>
+          <t>no_kis_pbi</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       <c r="G66" s="4" t="inlineStr"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Tinggi badan dalam cm (butir 21)</t>
+          <t>Nomor KIS Penerima Bantuan Iuran (butir 20)</t>
         </is>
       </c>
     </row>
@@ -2901,16 +2901,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>berat_badan_kg</t>
+          <t>tinggi_badan_cm</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>numeric(4,1)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr"/>
@@ -2922,7 +2922,7 @@
       <c r="G67" s="4" t="inlineStr"/>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>Berat badan dalam kg (butir 22)</t>
+          <t>Tinggi badan dalam cm (butir 21)</t>
         </is>
       </c>
     </row>
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>waktu_ke_sekolah_menit</t>
+          <t>berat_badan_kg</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>numeric(4,1)</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr"/>
@@ -2954,7 +2954,7 @@
       <c r="G68" s="4" t="inlineStr"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Waktu tempuh ke sekolah dalam menit (butir 24)</t>
+          <t>Berat badan dalam kg (butir 22)</t>
         </is>
       </c>
     </row>
@@ -2965,32 +2965,28 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>berkebutuhan_khusus</t>
+          <t>waktu_ke_sekolah_menit</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr"/>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Jenis kebutuhan khusus, bila ada</t>
+          <t>Waktu tempuh ke sekolah dalam menit (butir 24)</t>
         </is>
       </c>
     </row>
@@ -3001,16 +2997,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>dibuat_pada</t>
+          <t>berkebutuhan_khusus</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr"/>
@@ -3021,12 +3017,12 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>now()</t>
+          <t>false</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>Waktu data dibuat</t>
+          <t>Jenis kebutuhan khusus, bila ada</t>
         </is>
       </c>
     </row>
@@ -3037,11 +3033,11 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>diubah_pada</t>
+          <t>dibuat_pada</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3062,83 +3058,83 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
+          <t>Waktu data dibuat</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CALON_MURID</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>diubah_pada</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
           <t>Waktu data terakhir diubah</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>ORANG_TUA_WALI</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n">
+      <c r="B73" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.orang_tua_wali_id_seq)</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>ORANG_TUA_WALI</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>calon_murid_id</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>UK, FK → calon_murid</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr"/>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Calon murid terkait</t>
         </is>
       </c>
     </row>
@@ -3149,21 +3145,21 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>hubungan</t>
+          <t>calon_murid_id</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>hubungan_keluarga</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UK, FK → calon_murid</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3174,7 +3170,7 @@
       <c r="G74" s="4" t="inlineStr"/>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Hubungan: ayah, ibu, wali</t>
+          <t>Calon murid terkait</t>
         </is>
       </c>
     </row>
@@ -3185,19 +3181,23 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>nama</t>
+          <t>hubungan</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr"/>
+          <t>hubungan_keluarga</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -3206,7 +3206,7 @@
       <c r="G75" s="4" t="inlineStr"/>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Nama ayah/ibu/wali</t>
+          <t>Hubungan: ayah, ibu, wali</t>
         </is>
       </c>
     </row>
@@ -3217,28 +3217,28 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>nik</t>
+          <t>nama</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>character(16)</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Nomor Induk Kependudukan (16 digit)</t>
+          <t>Nama ayah/ibu/wali</t>
         </is>
       </c>
     </row>
@@ -3249,16 +3249,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>tahun_lahir</t>
+          <t>nik</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>character(16)</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr"/>
@@ -3270,7 +3270,7 @@
       <c r="G77" s="4" t="inlineStr"/>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Tahun lahir orang tua/wali</t>
+          <t>Nomor Induk Kependudukan (16 digit)</t>
         </is>
       </c>
     </row>
@@ -3281,16 +3281,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>pendidikan</t>
+          <t>tahun_lahir</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>varchar(30)</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr"/>
@@ -3302,7 +3302,7 @@
       <c r="G78" s="4" t="inlineStr"/>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>Pendidikan terakhir</t>
+          <t>Tahun lahir orang tua/wali</t>
         </is>
       </c>
     </row>
@@ -3313,16 +3313,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>pekerjaan</t>
+          <t>pendidikan</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>varchar(60)</t>
+          <t>varchar(30)</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr"/>
@@ -3334,7 +3334,7 @@
       <c r="G79" s="4" t="inlineStr"/>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>Pekerjaan</t>
+          <t>Pendidikan terakhir</t>
         </is>
       </c>
     </row>
@@ -3345,16 +3345,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>penghasilan</t>
+          <t>pekerjaan</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>varchar(40)</t>
+          <t>varchar(60)</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr"/>
@@ -3366,7 +3366,7 @@
       <c r="G80" s="4" t="inlineStr"/>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Rentang penghasilan per bulan</t>
+          <t>Pekerjaan</t>
         </is>
       </c>
     </row>
@@ -3377,16 +3377,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>no_hp</t>
+          <t>penghasilan</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>varchar(15)</t>
+          <t>varchar(40)</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr"/>
@@ -3398,83 +3398,79 @@
       <c r="G81" s="4" t="inlineStr"/>
       <c r="H81" s="4" t="inlineStr">
         <is>
+          <t>Rentang penghasilan per bulan</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>ORANG_TUA_WALI</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>no_hp</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>varchar(15)</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
           <t>Nomor HP/WhatsApp, diawali 08</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>PENDAFTARAN</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n">
+      <c r="B83" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.pendaftaran_id_seq)</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
-        <is>
-          <t>PENDAFTARAN</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>nomor_pendaftaran</t>
-        </is>
-      </c>
-      <c r="D83" s="4" t="inlineStr">
-        <is>
-          <t>varchar(25)</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>Nomor pendaftaran unik, terisi saat diajukan</t>
         </is>
       </c>
     </row>
@@ -3485,32 +3481,32 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>calon_murid_id</t>
+          <t>nomor_pendaftaran</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(25)</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>UK, FK → calon_murid</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr"/>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>Calon murid terkait</t>
+          <t>Nomor pendaftaran unik, terisi saat diajukan</t>
         </is>
       </c>
     </row>
@@ -3521,11 +3517,11 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>periode_id</t>
+          <t>calon_murid_id</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3535,7 +3531,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>UK, FK → periode_spmb</t>
+          <t>UK, FK → calon_murid</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3546,7 +3542,7 @@
       <c r="G85" s="4" t="inlineStr"/>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>Periode SPMB terkait</t>
+          <t>Calon murid terkait</t>
         </is>
       </c>
     </row>
@@ -3557,19 +3553,23 @@
         </is>
       </c>
       <c r="B86" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>jalur</t>
+          <t>periode_id</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>jalur_spmb</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>UK, FK → periode_spmb</t>
+        </is>
+      </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -3578,7 +3578,7 @@
       <c r="G86" s="4" t="inlineStr"/>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Jalur pendaftaran: domisili, afirmasi, mutasi</t>
+          <t>Periode SPMB terkait</t>
         </is>
       </c>
     </row>
@@ -3589,16 +3589,16 @@
         </is>
       </c>
       <c r="B87" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>jalur</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>status_pendaftaran</t>
+          <t>jalur_spmb</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr"/>
@@ -3607,14 +3607,10 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>'draf'</t>
-        </is>
-      </c>
+      <c r="G87" s="4" t="inlineStr"/>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Status: draf, diajukan, perlu_perbaikan, terverifikasi, diterima, tidak_diterima</t>
+          <t>Jalur pendaftaran: domisili, afirmasi, mutasi</t>
         </is>
       </c>
     </row>
@@ -3625,28 +3621,32 @@
         </is>
       </c>
       <c r="B88" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>usia_bulan</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>status_pendaftaran</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr"/>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="inlineStr"/>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>'draf'</t>
+        </is>
+      </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Usia calon murid (bulan) pada tanggal acuan</t>
+          <t>Status: draf, diajukan, perlu_perbaikan, terverifikasi, diterima, tidak_diterima</t>
         </is>
       </c>
     </row>
@@ -3657,32 +3657,28 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>perlu_rekomendasi_psikolog</t>
+          <t>usia_bulan</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr"/>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr"/>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Usia 5 th 6 bln – &lt; 6 th, wajib rekomendasi psikolog</t>
+          <t>Usia calon murid (bulan) pada tanggal acuan</t>
         </is>
       </c>
     </row>
@@ -3693,28 +3689,32 @@
         </is>
       </c>
       <c r="B90" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>catatan_panitia</t>
+          <t>perlu_rekomendasi_psikolog</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr"/>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="inlineStr"/>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>Catatan panitia untuk perbaikan</t>
+          <t>Usia 5 th 6 bln – &lt; 6 th, wajib rekomendasi psikolog</t>
         </is>
       </c>
     </row>
@@ -3725,16 +3725,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>peringkat</t>
+          <t>catatan_panitia</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>smallint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       <c r="G91" s="4" t="inlineStr"/>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>Urutan hasil seleksi dalam jalurnya (usia → jarak → waktu daftar)</t>
+          <t>Catatan panitia untuk perbaikan</t>
         </is>
       </c>
     </row>
@@ -3757,16 +3757,16 @@
         </is>
       </c>
       <c r="B92" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>diajukan_pada</t>
+          <t>peringkat</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>smallint</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr"/>
@@ -3778,7 +3778,7 @@
       <c r="G92" s="4" t="inlineStr"/>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>Waktu pendaftaran diajukan</t>
+          <t>Urutan hasil seleksi dalam jalurnya (usia → jarak → waktu daftar)</t>
         </is>
       </c>
     </row>
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>daftar_ulang_pada</t>
+          <t>diajukan_pada</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3810,7 +3810,7 @@
       <c r="G93" s="4" t="inlineStr"/>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Waktu orang tua mengonfirmasi daftar ulang</t>
+          <t>Waktu pendaftaran diajukan</t>
         </is>
       </c>
     </row>
@@ -3821,11 +3821,11 @@
         </is>
       </c>
       <c r="B94" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>dibuat_pada</t>
+          <t>daftar_ulang_pada</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3836,17 +3836,13 @@
       <c r="E94" s="4" t="inlineStr"/>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G94" s="4" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr"/>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Waktu data dibuat</t>
+          <t>Waktu orang tua mengonfirmasi daftar ulang</t>
         </is>
       </c>
     </row>
@@ -3857,11 +3853,11 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>diubah_pada</t>
+          <t>dibuat_pada</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3882,83 +3878,83 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
+          <t>Waktu data dibuat</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>PENDAFTARAN</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>diubah_pada</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr"/>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
           <t>Waktu data terakhir diubah</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>DOKUMEN</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n">
+      <c r="B97" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.dokumen_id_seq)</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>DOKUMEN</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>pendaftaran_id</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>UK, FK → pendaftaran</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr"/>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Pendaftaran terkait</t>
         </is>
       </c>
     </row>
@@ -3969,11 +3965,11 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>jenis_dokumen_id</t>
+          <t>pendaftaran_id</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3983,7 +3979,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>UK, FK → jenis_dokumen</t>
+          <t>UK, FK → pendaftaran</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3994,7 +3990,7 @@
       <c r="G98" s="4" t="inlineStr"/>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Jenis dokumen terkait</t>
+          <t>Pendaftaran terkait</t>
         </is>
       </c>
     </row>
@@ -4005,19 +4001,23 @@
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>nama_file_asli</t>
+          <t>jenis_dokumen_id</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>varchar(200)</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>UK, FK → jenis_dokumen</t>
+        </is>
+      </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
           <t>Ya</t>
@@ -4026,7 +4026,7 @@
       <c r="G99" s="4" t="inlineStr"/>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Nama berkas asli dari pengguna</t>
+          <t>Jenis dokumen terkait</t>
         </is>
       </c>
     </row>
@@ -4037,16 +4037,16 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>path_file</t>
+          <t>nama_file_asli</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>varchar(255)</t>
+          <t>varchar(200)</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       <c r="G100" s="4" t="inlineStr"/>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Nama berkas acak di server</t>
+          <t>Nama berkas asli dari pengguna</t>
         </is>
       </c>
     </row>
@@ -4069,16 +4069,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>tipe_mime</t>
+          <t>path_file</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>varchar(50)</t>
+          <t>varchar(255)</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
       <c r="G101" s="4" t="inlineStr"/>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>Tipe berkas (PDF/JPG/PNG)</t>
+          <t>Nama berkas acak di server</t>
         </is>
       </c>
     </row>
@@ -4101,16 +4101,16 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>ukuran_byte</t>
+          <t>tipe_mime</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>varchar(50)</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -4122,7 +4122,7 @@
       <c r="G102" s="4" t="inlineStr"/>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>Ukuran berkas (maks. 2 MB)</t>
+          <t>Tipe berkas (PDF/JPG/PNG)</t>
         </is>
       </c>
     </row>
@@ -4133,16 +4133,16 @@
         </is>
       </c>
       <c r="B103" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>status_verifikasi</t>
+          <t>ukuran_byte</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>status_dokumen</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -4151,14 +4151,10 @@
           <t>Ya</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>'menunggu'</t>
-        </is>
-      </c>
+      <c r="G103" s="4" t="inlineStr"/>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>Status verifikasi dokumen: menunggu, valid, tidak_valid</t>
+          <t>Ukuran berkas (maks. 2 MB)</t>
         </is>
       </c>
     </row>
@@ -4169,28 +4165,32 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>catatan</t>
+          <t>status_verifikasi</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>status_dokumen</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr"/>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr"/>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>'menunggu'</t>
+        </is>
+      </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Catatan verifikasi dari panitia</t>
+          <t>Status verifikasi dokumen: menunggu, valid, tidak_valid</t>
         </is>
       </c>
     </row>
@@ -4201,108 +4201,104 @@
         </is>
       </c>
       <c r="B105" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>diunggah_pada</t>
+          <t>catatan</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr"/>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Catatan verifikasi dari panitia</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>DOKUMEN</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>diunggah_pada</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="H105" s="4" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>Waktu unggah</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>RIWAYAT_STATUS</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n">
+      <c r="B107" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>bigint</t>
         </is>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
         <is>
           <t>serial (spmb.riwayat_status_id_seq)</t>
         </is>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H107" s="6" t="inlineStr">
         <is>
           <t>Kunci utama (nomor urut otomatis)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="4" t="inlineStr">
-        <is>
-          <t>RIWAYAT_STATUS</t>
-        </is>
-      </c>
-      <c r="B107" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C107" s="4" t="inlineStr">
-        <is>
-          <t>pendaftaran_id</t>
-        </is>
-      </c>
-      <c r="D107" s="4" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>FK → pendaftaran</t>
-        </is>
-      </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G107" s="4" t="inlineStr"/>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>Pendaftaran terkait</t>
         </is>
       </c>
     </row>
@@ -4313,28 +4309,32 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>status_lama</t>
+          <t>pendaftaran_id</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>status_pendaftaran</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>FK → pendaftaran</t>
+        </is>
+      </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>Status sebelum berubah</t>
+          <t>Pendaftaran terkait</t>
         </is>
       </c>
     </row>
@@ -4345,11 +4345,11 @@
         </is>
       </c>
       <c r="B109" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>status_baru</t>
+          <t>status_lama</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -4360,13 +4360,13 @@
       <c r="E109" s="4" t="inlineStr"/>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
+          <t>Tidak</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>Status sesudah berubah</t>
+          <t>Status sebelum berubah</t>
         </is>
       </c>
     </row>
@@ -4377,32 +4377,28 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>oleh_pengguna_id</t>
+          <t>status_baru</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>FK → pengguna</t>
-        </is>
-      </c>
+          <t>status_pendaftaran</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Tidak</t>
+          <t>Ya</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>Pengguna yang mengubah status</t>
+          <t>Status sesudah berubah</t>
         </is>
       </c>
     </row>
@@ -4413,19 +4409,23 @@
         </is>
       </c>
       <c r="B111" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>catatan</t>
+          <t>oleh_pengguna_id</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr"/>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>FK → pengguna</t>
+        </is>
+      </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
           <t>Tidak</t>
@@ -4434,7 +4434,7 @@
       <c r="G111" s="4" t="inlineStr"/>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>Catatan alasan perubahan status</t>
+          <t>Pengguna yang mengubah status</t>
         </is>
       </c>
     </row>
@@ -4445,37 +4445,69 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>waktu</t>
+          <t>catatan</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>timestamptz</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Ya</t>
-        </is>
-      </c>
-      <c r="G112" s="4" t="inlineStr">
+          <t>Tidak</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr"/>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>Catatan alasan perubahan status</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>RIWAYAT_STATUS</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>waktu</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>timestamptz</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Ya</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>now()</t>
         </is>
       </c>
-      <c r="H112" s="4" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>Waktu perubahan status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H112"/>
+  <autoFilter ref="A4:H113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
